--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.6784,0.1830,0.1798,0.0791</t>
-  </si>
-  <si>
-    <t>0.0019,0.0055,0.0047,0.9971</t>
-  </si>
-  <si>
-    <t>0.3662,0.1472,0.0066,0.4890</t>
-  </si>
-  <si>
-    <t>0.0175,0.0260,0.0096,0.9862</t>
-  </si>
-  <si>
-    <t>0.9776,0.0216,0.0039,0.0009</t>
-  </si>
-  <si>
-    <t>0.9726,0.0226,0.0027,0.0021</t>
-  </si>
-  <si>
-    <t>0.9757,0.0201,0.0056,0.0015</t>
-  </si>
-  <si>
-    <t>0.9804,0.0090,0.0095,0.0016</t>
-  </si>
-  <si>
-    <t>0.9817,0.0204,0.0023,0.0007</t>
-  </si>
-  <si>
-    <t>0.9663,0.0332,0.0058,0.0012</t>
-  </si>
-  <si>
-    <t>0.9864,0.0058,0.0015,0.0021</t>
-  </si>
-  <si>
-    <t>0.9751,0.0168,0.0041,0.0031</t>
-  </si>
-  <si>
-    <t>0.4434,0.2682,0.3621,0.1147</t>
-  </si>
-  <si>
-    <t>0.0615,0.0586,0.9132,0.0041</t>
-  </si>
-  <si>
-    <t>0.1264,0.0574,0.8632,0.0092</t>
-  </si>
-  <si>
-    <t>0.0773,0.1873,0.7651,0.0234</t>
-  </si>
-  <si>
-    <t>0.3882,0.0473,0.6917,0.0253</t>
-  </si>
-  <si>
-    <t>0.0909,0.9107,0.0243,0.0027</t>
-  </si>
-  <si>
-    <t>0.0397,0.9447,0.0304,0.0006</t>
-  </si>
-  <si>
-    <t>0.3697,0.7188,0.0190,0.0036</t>
-  </si>
-  <si>
-    <t>0.1104,0.9020,0.0164,0.0012</t>
-  </si>
-  <si>
-    <t>0.0420,0.9494,0.0147,0.0012</t>
-  </si>
-  <si>
-    <t>0.4024,0.0820,0.5689,0.0855</t>
-  </si>
-  <si>
-    <t>0.0919,0.1359,0.7669,0.0267</t>
-  </si>
-  <si>
-    <t>0.0075,0.0057,0.9779,0.0150</t>
-  </si>
-  <si>
-    <t>0.1248,0.0157,0.8991,0.0112</t>
-  </si>
-  <si>
-    <t>0.0252,0.0090,0.9771,0.0023</t>
-  </si>
-  <si>
-    <t>0.0927,0.0246,0.8875,0.0164</t>
-  </si>
-  <si>
-    <t>0.0005,0.0006,0.9923,0.0300</t>
-  </si>
-  <si>
-    <t>0.2127,0.8345,0.0207,0.0021</t>
-  </si>
-  <si>
-    <t>0.4106,0.1997,0.5088,0.0203</t>
-  </si>
-  <si>
-    <t>0.0008,0.0033,0.9948,0.0068</t>
-  </si>
-  <si>
-    <t>0.0300,0.3308,0.8252,0.0019</t>
-  </si>
-  <si>
-    <t>0.2306,0.7893,0.0312,0.0149</t>
-  </si>
-  <si>
-    <t>0.1947,0.5734,0.2852,0.0111</t>
-  </si>
-  <si>
-    <t>0.2344,0.7804,0.0503,0.0022</t>
-  </si>
-  <si>
-    <t>0.0129,0.7151,0.8114,0.0041</t>
-  </si>
-  <si>
-    <t>0.0043,0.3256,0.8802,0.0136</t>
-  </si>
-  <si>
-    <t>0.0018,0.0780,0.9701,0.0078</t>
-  </si>
-  <si>
-    <t>0.0024,0.5089,0.9369,0.0018</t>
-  </si>
-  <si>
-    <t>0.0034,0.0034,0.9869,0.0107</t>
-  </si>
-  <si>
-    <t>0.0073,0.1801,0.9463,0.0036</t>
-  </si>
-  <si>
-    <t>0.0091,0.8520,0.5164,0.0030</t>
-  </si>
-  <si>
-    <t>0.0072,0.0402,0.9728,0.0041</t>
-  </si>
-  <si>
-    <t>0.4699,0.2453,0.2870,0.2452</t>
-  </si>
-  <si>
-    <t>0.0032,0.9750,0.0338,0.0055</t>
-  </si>
-  <si>
-    <t>0.0019,0.9686,0.2334,0.0021</t>
-  </si>
-  <si>
-    <t>0.0011,0.9781,0.0473,0.0042</t>
-  </si>
-  <si>
-    <t>0.0006,0.1545,0.9873,0.0021</t>
-  </si>
-  <si>
-    <t>0.0008,0.2378,0.9820,0.0022</t>
-  </si>
-  <si>
-    <t>0.0806,0.0563,0.8708,0.0324</t>
-  </si>
-  <si>
-    <t>0.0214,0.0156,0.9618,0.0065</t>
-  </si>
-  <si>
-    <t>0.0066,0.0173,0.9800,0.0066</t>
-  </si>
-  <si>
-    <t>0.0030,0.0137,0.9898,0.0013</t>
-  </si>
-  <si>
-    <t>0.8699,0.1595,0.0146,0.0040</t>
-  </si>
-  <si>
-    <t>0.9406,0.0472,0.0170,0.0049</t>
-  </si>
-  <si>
-    <t>0.9606,0.0267,0.0072,0.0041</t>
-  </si>
-  <si>
-    <t>0.0099,0.0797,0.9780,0.0029</t>
-  </si>
-  <si>
-    <t>0.9412,0.0607,0.0076,0.0024</t>
-  </si>
-  <si>
-    <t>0.7445,0.3179,0.0198,0.0040</t>
-  </si>
-  <si>
-    <t>0.6964,0.3522,0.0216,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.6312,0.9854,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.1961,0.9872,0.0003</t>
-  </si>
-  <si>
-    <t>0.0084,0.2173,0.8931,0.0302</t>
-  </si>
-  <si>
-    <t>0.0001,0.9055,0.9525,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0197,0.9962,0.0013</t>
-  </si>
-  <si>
-    <t>0.0148,0.9511,0.0967,0.0014</t>
-  </si>
-  <si>
-    <t>0.0020,0.9894,0.0354,0.0003</t>
-  </si>
-  <si>
-    <t>0.3589,0.1106,0.6616,0.0149</t>
-  </si>
-  <si>
-    <t>0.4217,0.3694,0.2988,0.0245</t>
-  </si>
-  <si>
-    <t>0.0019,0.0978,0.9892,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.9564,0.9124,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.7957,0.9000,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.9237,0.7812,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.7969,0.9706,0.0001</t>
-  </si>
-  <si>
-    <t>0.0310,0.0450,0.0410,0.9589</t>
-  </si>
-  <si>
-    <t>0.0019,0.0101,0.0041,0.9971</t>
-  </si>
-  <si>
-    <t>0.0020,0.0093,0.0030,0.9973</t>
-  </si>
-  <si>
-    <t>0.0147,0.0396,0.0330,0.9706</t>
-  </si>
-  <si>
-    <t>0.0108,0.0097,0.0115,0.9875</t>
-  </si>
-  <si>
-    <t>0.0031,0.0069,0.0028,0.9969</t>
-  </si>
-  <si>
-    <t>0.0014,0.7530,0.9245,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.6882,0.9625,0.0004</t>
-  </si>
-  <si>
-    <t>0.0063,0.5509,0.8704,0.0045</t>
-  </si>
-  <si>
-    <t>0.0012,0.8077,0.8974,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.9185,0.9158,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.7597,0.9435,0.0002</t>
-  </si>
-  <si>
-    <t>0.9466,0.0442,0.0183,0.0017</t>
-  </si>
-  <si>
-    <t>0.7368,0.2891,0.0344,0.0020</t>
-  </si>
-  <si>
-    <t>0.8981,0.1209,0.0112,0.0025</t>
-  </si>
-  <si>
-    <t>0.9853,0.0065,0.0020,0.0021</t>
-  </si>
-  <si>
-    <t>0.9615,0.0363,0.0045,0.0025</t>
-  </si>
-  <si>
-    <t>0.9671,0.0297,0.0060,0.0015</t>
-  </si>
-  <si>
-    <t>0.9629,0.0257,0.0018,0.0047</t>
-  </si>
-  <si>
-    <t>0.9786,0.0139,0.0045,0.0023</t>
-  </si>
-  <si>
-    <t>0.9823,0.0106,0.0023,0.0022</t>
-  </si>
-  <si>
-    <t>0.9844,0.0116,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.9807,0.0097,0.0034,0.0025</t>
-  </si>
-  <si>
-    <t>0.9724,0.0211,0.0053,0.0020</t>
-  </si>
-  <si>
-    <t>0.9882,0.0058,0.0011,0.0016</t>
-  </si>
-  <si>
-    <t>0.9902,0.0054,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.9598,0.0461,0.0033,0.0017</t>
-  </si>
-  <si>
-    <t>0.9833,0.0136,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.0003,0.0031,0.9974,0.0021</t>
-  </si>
-  <si>
-    <t>0.0259,0.0201,0.9415,0.0120</t>
-  </si>
-  <si>
-    <t>0.3925,0.0727,0.2545,0.3766</t>
-  </si>
-  <si>
-    <t>0.0876,0.1067,0.8460,0.0419</t>
-  </si>
-  <si>
-    <t>0.0780,0.9139,0.0241,0.0010</t>
-  </si>
-  <si>
-    <t>0.0510,0.9141,0.0623,0.0008</t>
-  </si>
-  <si>
-    <t>0.0905,0.9120,0.0092,0.0029</t>
-  </si>
-  <si>
-    <t>0.4253,0.7323,0.0047,0.0018</t>
-  </si>
-  <si>
-    <t>0.0472,0.9389,0.0268,0.0008</t>
-  </si>
-  <si>
-    <t>0.0332,0.9615,0.0119,0.0002</t>
-  </si>
-  <si>
-    <t>0.3152,0.7590,0.0191,0.0014</t>
-  </si>
-  <si>
-    <t>0.3823,0.1502,0.5599,0.0207</t>
-  </si>
-  <si>
-    <t>0.0428,0.0157,0.9561,0.0028</t>
-  </si>
-  <si>
-    <t>0.1672,0.5874,0.2785,0.1462</t>
-  </si>
-  <si>
-    <t>0.1238,0.1200,0.7973,0.0127</t>
-  </si>
-  <si>
-    <t>0.2472,0.5668,0.1142,0.2673</t>
-  </si>
-  <si>
-    <t>0.0028,0.9803,0.0878,0.0008</t>
-  </si>
-  <si>
-    <t>0.0049,0.9713,0.0402,0.0041</t>
-  </si>
-  <si>
-    <t>0.0223,0.9246,0.0176,0.0464</t>
-  </si>
-  <si>
-    <t>0.0002,0.9560,0.9086,0.0001</t>
-  </si>
-  <si>
-    <t>0.0368,0.8700,0.2532,0.0012</t>
-  </si>
-  <si>
-    <t>0.2203,0.8073,0.0304,0.0025</t>
-  </si>
-  <si>
-    <t>0.1198,0.7977,0.1243,0.0024</t>
-  </si>
-  <si>
-    <t>0.8587,0.1129,0.0565,0.0113</t>
-  </si>
-  <si>
-    <t>0.9791,0.0058,0.0019,0.0068</t>
-  </si>
-  <si>
-    <t>0.9593,0.0119,0.0046,0.0147</t>
-  </si>
-  <si>
-    <t>0.9741,0.0131,0.0036,0.0034</t>
-  </si>
-  <si>
-    <t>0.9310,0.0660,0.0084,0.0048</t>
-  </si>
-  <si>
-    <t>0.9409,0.0264,0.0402,0.0066</t>
-  </si>
-  <si>
-    <t>0.9704,0.0163,0.0082,0.0033</t>
-  </si>
-  <si>
-    <t>0.9696,0.0191,0.0038,0.0034</t>
-  </si>
-  <si>
-    <t>0.0029,0.4587,0.9542,0.0017</t>
-  </si>
-  <si>
-    <t>0.0004,0.6848,0.9674,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0208,0.9916,0.0005</t>
-  </si>
-  <si>
-    <t>0.0061,0.0585,0.9745,0.0034</t>
-  </si>
-  <si>
-    <t>0.4782,0.2771,0.0550,0.2782</t>
-  </si>
-  <si>
-    <t>0.3893,0.4260,0.1774,0.2215</t>
-  </si>
-  <si>
-    <t>0.1906,0.0466,0.8195,0.0120</t>
-  </si>
-  <si>
-    <t>0.0513,0.2243,0.8283,0.0092</t>
-  </si>
-  <si>
-    <t>0.0444,0.0435,0.0096,0.9692</t>
-  </si>
-  <si>
-    <t>0.0001,0.0020,0.0024,0.9995</t>
-  </si>
-  <si>
-    <t>0.0024,0.0109,0.0023,0.9974</t>
-  </si>
-  <si>
-    <t>0.0121,0.0021,0.0299,0.9793</t>
-  </si>
-  <si>
-    <t>0.0035,0.7094,0.8593,0.0023</t>
-  </si>
-  <si>
-    <t>0.9240,0.0825,0.0110,0.0025</t>
-  </si>
-  <si>
-    <t>0.3661,0.6414,0.0623,0.0133</t>
-  </si>
-  <si>
-    <t>0.9090,0.0644,0.0077,0.0118</t>
-  </si>
-  <si>
-    <t>0.3725,0.6350,0.0531,0.0052</t>
-  </si>
-  <si>
-    <t>0.7610,0.1895,0.0838,0.0117</t>
-  </si>
-  <si>
-    <t>0.2628,0.0172,0.5461,0.2372</t>
-  </si>
-  <si>
-    <t>0.9712,0.0091,0.0060,0.0071</t>
-  </si>
-  <si>
-    <t>0.0101,0.2563,0.9472,0.0080</t>
-  </si>
-  <si>
-    <t>0.4374,0.0057,0.1089,0.4219</t>
-  </si>
-  <si>
-    <t>0.9107,0.0304,0.0530,0.0148</t>
-  </si>
-  <si>
-    <t>0.2708,0.7611,0.0355,0.0204</t>
-  </si>
-  <si>
-    <t>0.7301,0.1817,0.1703,0.0369</t>
-  </si>
-  <si>
-    <t>0.7097,0.1139,0.2830,0.0296</t>
-  </si>
-  <si>
-    <t>0.3740,0.6226,0.0652,0.0214</t>
-  </si>
-  <si>
-    <t>0.1568,0.7646,0.1215,0.0104</t>
-  </si>
-  <si>
-    <t>0.2944,0.6370,0.1877,0.0370</t>
-  </si>
-  <si>
-    <t>0.9513,0.0365,0.0079,0.0047</t>
-  </si>
-  <si>
-    <t>0.9288,0.0881,0.0060,0.0020</t>
-  </si>
-  <si>
-    <t>0.9640,0.0373,0.0060,0.0015</t>
-  </si>
-  <si>
-    <t>0.9599,0.0260,0.0143,0.0034</t>
-  </si>
-  <si>
-    <t>0.8963,0.1209,0.0071,0.0038</t>
-  </si>
-  <si>
-    <t>0.9023,0.1420,0.0035,0.0021</t>
-  </si>
-  <si>
-    <t>0.9467,0.0223,0.0064,0.0124</t>
-  </si>
-  <si>
-    <t>0.9831,0.0091,0.0026,0.0018</t>
-  </si>
-  <si>
-    <t>0.0749,0.9307,0.0096,0.0011</t>
-  </si>
-  <si>
-    <t>0.4737,0.6342,0.0141,0.0007</t>
-  </si>
-  <si>
-    <t>0.4882,0.5527,0.0444,0.0024</t>
-  </si>
-  <si>
-    <t>0.0584,0.2122,0.8664,0.0046</t>
-  </si>
-  <si>
-    <t>0.9193,0.0762,0.0074,0.0052</t>
-  </si>
-  <si>
-    <t>0.6120,0.4617,0.0285,0.0064</t>
-  </si>
-  <si>
-    <t>0.9348,0.0890,0.0056,0.0015</t>
-  </si>
-  <si>
-    <t>0.6964,0.2664,0.0851,0.0054</t>
-  </si>
-  <si>
-    <t>0.0033,0.0551,0.9900,0.0009</t>
-  </si>
-  <si>
-    <t>0.6641,0.3417,0.0536,0.0024</t>
-  </si>
-  <si>
-    <t>0.0024,0.0167,0.9901,0.0007</t>
-  </si>
-  <si>
-    <t>0.0034,0.2609,0.9647,0.0035</t>
-  </si>
-  <si>
-    <t>0.0496,0.0118,0.9456,0.0134</t>
-  </si>
-  <si>
-    <t>0.0027,0.0968,0.9844,0.0020</t>
-  </si>
-  <si>
-    <t>0.0152,0.0182,0.9671,0.0066</t>
-  </si>
-  <si>
-    <t>0.0011,0.0033,0.9962,0.0004</t>
-  </si>
-  <si>
-    <t>0.0060,0.0298,0.9791,0.0064</t>
-  </si>
-  <si>
-    <t>0.1043,0.4340,0.5576,0.0103</t>
-  </si>
-  <si>
-    <t>0.2062,0.0214,0.8573,0.0129</t>
-  </si>
-  <si>
-    <t>0.2233,0.0722,0.7737,0.0090</t>
-  </si>
-  <si>
-    <t>0.0683,0.6829,0.3550,0.0030</t>
-  </si>
-  <si>
-    <t>0.0569,0.5990,0.5766,0.0106</t>
-  </si>
-  <si>
-    <t>0.1396,0.0827,0.8313,0.0070</t>
-  </si>
-  <si>
-    <t>0.2638,0.2060,0.5820,0.0156</t>
-  </si>
-  <si>
-    <t>0.1445,0.3991,0.5921,0.0138</t>
-  </si>
-  <si>
-    <t>0.7609,0.3021,0.0192,0.0027</t>
-  </si>
-  <si>
-    <t>0.6196,0.3995,0.0354,0.0014</t>
-  </si>
-  <si>
-    <t>0.5406,0.5170,0.0321,0.0046</t>
-  </si>
-  <si>
-    <t>0.9463,0.0568,0.0096,0.0016</t>
-  </si>
-  <si>
-    <t>0.8710,0.1907,0.0093,0.0021</t>
-  </si>
-  <si>
-    <t>0.1729,0.1113,0.7598,0.0129</t>
-  </si>
-  <si>
-    <t>0.4573,0.0492,0.6236,0.0226</t>
-  </si>
-  <si>
-    <t>0.3582,0.0946,0.6403,0.0579</t>
-  </si>
-  <si>
-    <t>0.3879,0.0431,0.5407,0.1359</t>
-  </si>
-  <si>
-    <t>0.4393,0.0669,0.5560,0.0906</t>
-  </si>
-  <si>
-    <t>0.0113,0.0210,0.9651,0.0215</t>
-  </si>
-  <si>
-    <t>0.0059,0.0784,0.9525,0.0202</t>
-  </si>
-  <si>
-    <t>0.0023,0.3217,0.9610,0.0029</t>
-  </si>
-  <si>
-    <t>0.0027,0.3475,0.9561,0.0032</t>
-  </si>
-  <si>
-    <t>0.0012,0.5413,0.9588,0.0007</t>
-  </si>
-  <si>
-    <t>0.9584,0.0378,0.0062,0.0030</t>
-  </si>
-  <si>
-    <t>0.9824,0.0116,0.0031,0.0015</t>
-  </si>
-  <si>
-    <t>0.9631,0.0328,0.0083,0.0020</t>
-  </si>
-  <si>
-    <t>0.9343,0.0708,0.0082,0.0025</t>
-  </si>
-  <si>
-    <t>0.9557,0.0324,0.0102,0.0044</t>
-  </si>
-  <si>
-    <t>0.9714,0.0309,0.0028,0.0012</t>
-  </si>
-  <si>
-    <t>0.9281,0.0627,0.0146,0.0038</t>
-  </si>
-  <si>
-    <t>0.9454,0.0371,0.0245,0.0039</t>
-  </si>
-  <si>
-    <t>0.0206,0.0149,0.9753,0.0022</t>
-  </si>
-  <si>
-    <t>0.2646,0.0760,0.7610,0.0136</t>
-  </si>
-  <si>
-    <t>0.6080,0.3278,0.1198,0.0153</t>
-  </si>
-  <si>
-    <t>0.0053,0.0306,0.9781,0.0041</t>
-  </si>
-  <si>
-    <t>0.0001,0.0252,0.9968,0.0008</t>
-  </si>
-  <si>
-    <t>0.0030,0.0187,0.9893,0.0010</t>
-  </si>
-  <si>
-    <t>0.0011,0.0030,0.9901,0.0123</t>
-  </si>
-  <si>
-    <t>0.0109,0.0440,0.9609,0.0100</t>
-  </si>
-  <si>
-    <t>0.0004,0.0042,0.9880,0.0237</t>
-  </si>
-  <si>
-    <t>0.0046,0.0134,0.9842,0.0019</t>
-  </si>
-  <si>
-    <t>0.0203,0.0493,0.9586,0.0055</t>
-  </si>
-  <si>
-    <t>0.4582,0.2096,0.4052,0.0690</t>
-  </si>
-  <si>
-    <t>0.1425,0.0102,0.8908,0.0164</t>
-  </si>
-  <si>
-    <t>0.6220,0.0218,0.2567,0.1372</t>
-  </si>
-  <si>
-    <t>0.9586,0.0402,0.0050,0.0027</t>
-  </si>
-  <si>
-    <t>0.9676,0.0248,0.0079,0.0023</t>
-  </si>
-  <si>
-    <t>0.9233,0.0990,0.0079,0.0020</t>
-  </si>
-  <si>
-    <t>0.9489,0.0334,0.0297,0.0028</t>
-  </si>
-  <si>
-    <t>0.9573,0.0296,0.0118,0.0041</t>
-  </si>
-  <si>
-    <t>0.9909,0.0042,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.9688,0.0248,0.0072,0.0020</t>
-  </si>
-  <si>
-    <t>0.9537,0.0435,0.0105,0.0026</t>
-  </si>
-  <si>
-    <t>0.0187,0.0886,0.9312,0.0024</t>
-  </si>
-  <si>
-    <t>0.0002,0.0014,0.9985,0.0008</t>
-  </si>
-  <si>
-    <t>0.0005,0.0386,0.9913,0.0043</t>
-  </si>
-  <si>
-    <t>0.0816,0.1185,0.8116,0.0101</t>
-  </si>
-  <si>
-    <t>0.0025,0.0026,0.9917,0.0067</t>
-  </si>
-  <si>
-    <t>0.0096,0.0287,0.5064,0.7697</t>
-  </si>
-  <si>
-    <t>0.0293,0.0188,0.9553,0.0064</t>
-  </si>
-  <si>
-    <t>0.0053,0.0774,0.9532,0.0215</t>
-  </si>
-  <si>
-    <t>0.0690,0.0068,0.0217,0.9490</t>
-  </si>
-  <si>
-    <t>0.0016,0.0340,0.0024,0.9972</t>
-  </si>
-  <si>
-    <t>0.0117,0.0325,0.0039,0.9909</t>
-  </si>
-  <si>
-    <t>0.0025,0.0045,0.0024,0.9972</t>
-  </si>
-  <si>
-    <t>0.0012,0.0028,0.0041,0.9980</t>
-  </si>
-  <si>
-    <t>0.3129,0.1609,0.1638,0.5449</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.7348,0.0254,0.1665,0.0843</t>
+  </si>
+  <si>
+    <t>0.0040,0.0021,0.0064,0.9955</t>
+  </si>
+  <si>
+    <t>0.6340,0.2250,0.2234,0.0558</t>
+  </si>
+  <si>
+    <t>0.0626,0.0342,0.0231,0.9575</t>
+  </si>
+  <si>
+    <t>0.9680,0.0288,0.0045,0.0017</t>
+  </si>
+  <si>
+    <t>0.9597,0.0268,0.0130,0.0041</t>
+  </si>
+  <si>
+    <t>0.9812,0.0136,0.0023,0.0016</t>
+  </si>
+  <si>
+    <t>0.9778,0.0124,0.0061,0.0028</t>
+  </si>
+  <si>
+    <t>0.9774,0.0193,0.0060,0.0012</t>
+  </si>
+  <si>
+    <t>0.9493,0.0531,0.0075,0.0023</t>
+  </si>
+  <si>
+    <t>0.9866,0.0107,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9713,0.0233,0.0071,0.0018</t>
+  </si>
+  <si>
+    <t>0.4934,0.0519,0.5450,0.0402</t>
+  </si>
+  <si>
+    <t>0.0557,0.2698,0.7770,0.0042</t>
+  </si>
+  <si>
+    <t>0.1402,0.0642,0.8451,0.0066</t>
+  </si>
+  <si>
+    <t>0.0664,0.0866,0.8626,0.0059</t>
+  </si>
+  <si>
+    <t>0.5409,0.0712,0.5388,0.0351</t>
+  </si>
+  <si>
+    <t>0.0833,0.9068,0.0250,0.0039</t>
+  </si>
+  <si>
+    <t>0.0360,0.9592,0.0131,0.0006</t>
+  </si>
+  <si>
+    <t>0.2600,0.7425,0.0548,0.0020</t>
+  </si>
+  <si>
+    <t>0.0684,0.9340,0.0085,0.0013</t>
+  </si>
+  <si>
+    <t>0.0133,0.9757,0.0121,0.0004</t>
+  </si>
+  <si>
+    <t>0.0448,0.0107,0.8752,0.1794</t>
+  </si>
+  <si>
+    <t>0.2661,0.3296,0.4527,0.0756</t>
+  </si>
+  <si>
+    <t>0.0363,0.0104,0.9486,0.0187</t>
+  </si>
+  <si>
+    <t>0.2683,0.0979,0.6557,0.0477</t>
+  </si>
+  <si>
+    <t>0.1046,0.0196,0.9101,0.0104</t>
+  </si>
+  <si>
+    <t>0.0215,0.0058,0.9675,0.0142</t>
+  </si>
+  <si>
+    <t>0.0278,0.0126,0.9345,0.0479</t>
+  </si>
+  <si>
+    <t>0.0520,0.9458,0.0129,0.0010</t>
+  </si>
+  <si>
+    <t>0.2206,0.6057,0.2830,0.0301</t>
+  </si>
+  <si>
+    <t>0.0010,0.0188,0.9946,0.0021</t>
+  </si>
+  <si>
+    <t>0.0310,0.6168,0.6042,0.0017</t>
+  </si>
+  <si>
+    <t>0.5729,0.4145,0.0872,0.0228</t>
+  </si>
+  <si>
+    <t>0.4350,0.4897,0.1469,0.0349</t>
+  </si>
+  <si>
+    <t>0.1706,0.8721,0.0160,0.0017</t>
+  </si>
+  <si>
+    <t>0.0813,0.8517,0.1264,0.0055</t>
+  </si>
+  <si>
+    <t>0.0035,0.6559,0.7001,0.0407</t>
+  </si>
+  <si>
+    <t>0.0013,0.0233,0.9884,0.0048</t>
+  </si>
+  <si>
+    <t>0.0047,0.2339,0.9249,0.0164</t>
+  </si>
+  <si>
+    <t>0.0052,0.0054,0.9676,0.0518</t>
+  </si>
+  <si>
+    <t>0.0029,0.4053,0.9540,0.0012</t>
+  </si>
+  <si>
+    <t>0.0033,0.9302,0.4284,0.0015</t>
+  </si>
+  <si>
+    <t>0.0039,0.1880,0.9603,0.0028</t>
+  </si>
+  <si>
+    <t>0.0768,0.3129,0.5645,0.2846</t>
+  </si>
+  <si>
+    <t>0.0056,0.9659,0.0430,0.0089</t>
+  </si>
+  <si>
+    <t>0.0038,0.9042,0.5919,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.9726,0.3936,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.0777,0.9838,0.0028</t>
+  </si>
+  <si>
+    <t>0.0015,0.0467,0.9886,0.0016</t>
+  </si>
+  <si>
+    <t>0.0469,0.0726,0.8917,0.0225</t>
+  </si>
+  <si>
+    <t>0.0096,0.0290,0.9776,0.0029</t>
+  </si>
+  <si>
+    <t>0.0077,0.0184,0.9727,0.0141</t>
+  </si>
+  <si>
+    <t>0.0072,0.0577,0.9688,0.0013</t>
+  </si>
+  <si>
+    <t>0.8087,0.2204,0.0271,0.0053</t>
+  </si>
+  <si>
+    <t>0.9380,0.0519,0.0120,0.0053</t>
+  </si>
+  <si>
+    <t>0.8966,0.1053,0.0174,0.0062</t>
+  </si>
+  <si>
+    <t>0.0188,0.0874,0.9683,0.0024</t>
+  </si>
+  <si>
+    <t>0.9572,0.0450,0.0070,0.0018</t>
+  </si>
+  <si>
+    <t>0.9767,0.0163,0.0047,0.0024</t>
+  </si>
+  <si>
+    <t>0.7342,0.3709,0.0124,0.0024</t>
+  </si>
+  <si>
+    <t>0.0006,0.8147,0.9316,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0137,0.9924,0.0046</t>
+  </si>
+  <si>
+    <t>0.0028,0.0293,0.9819,0.0070</t>
+  </si>
+  <si>
+    <t>0.0000,0.8562,0.9854,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0227,0.9956,0.0008</t>
+  </si>
+  <si>
+    <t>0.0320,0.8676,0.2474,0.0045</t>
+  </si>
+  <si>
+    <t>0.0020,0.9904,0.0163,0.0003</t>
+  </si>
+  <si>
+    <t>0.2220,0.0679,0.8118,0.0071</t>
+  </si>
+  <si>
+    <t>0.2376,0.6279,0.1952,0.0066</t>
+  </si>
+  <si>
+    <t>0.0602,0.4359,0.7498,0.0129</t>
+  </si>
+  <si>
+    <t>0.0002,0.8805,0.9105,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.8859,0.9233,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9822,0.7878,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9106,0.9531,0.0001</t>
+  </si>
+  <si>
+    <t>0.0783,0.0092,0.3542,0.7145</t>
+  </si>
+  <si>
+    <t>0.0009,0.0082,0.0008,0.9989</t>
+  </si>
+  <si>
+    <t>0.0014,0.0099,0.0008,0.9986</t>
+  </si>
+  <si>
+    <t>0.0022,0.0051,0.0082,0.9962</t>
+  </si>
+  <si>
+    <t>0.0152,0.0152,0.0108,0.9854</t>
+  </si>
+  <si>
+    <t>0.0007,0.0060,0.0017,0.9988</t>
+  </si>
+  <si>
+    <t>0.0002,0.9571,0.8869,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.2654,0.9912,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.7310,0.8721,0.0012</t>
+  </si>
+  <si>
+    <t>0.0012,0.3327,0.9771,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9578,0.9526,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.5990,0.9379,0.0005</t>
+  </si>
+  <si>
+    <t>0.9422,0.0639,0.0105,0.0014</t>
+  </si>
+  <si>
+    <t>0.9660,0.0335,0.0078,0.0012</t>
+  </si>
+  <si>
+    <t>0.9406,0.0742,0.0085,0.0013</t>
+  </si>
+  <si>
+    <t>0.8911,0.1486,0.0071,0.0026</t>
+  </si>
+  <si>
+    <t>0.8351,0.1886,0.0191,0.0025</t>
+  </si>
+  <si>
+    <t>0.9900,0.0089,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9388,0.0904,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.9532,0.0586,0.0062,0.0011</t>
+  </si>
+  <si>
+    <t>0.9877,0.0085,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9821,0.0158,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.9898,0.0059,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9865,0.0085,0.0024,0.0011</t>
+  </si>
+  <si>
+    <t>0.9581,0.0329,0.0160,0.0027</t>
+  </si>
+  <si>
+    <t>0.9802,0.0177,0.0027,0.0014</t>
+  </si>
+  <si>
+    <t>0.9891,0.0057,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9919,0.0049,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.0020,0.9934,0.0113</t>
+  </si>
+  <si>
+    <t>0.0175,0.0338,0.9517,0.0070</t>
+  </si>
+  <si>
+    <t>0.5102,0.0584,0.4794,0.0740</t>
+  </si>
+  <si>
+    <t>0.0109,0.0283,0.9734,0.0020</t>
+  </si>
+  <si>
+    <t>0.1300,0.8769,0.0247,0.0017</t>
+  </si>
+  <si>
+    <t>0.0639,0.9315,0.0156,0.0017</t>
+  </si>
+  <si>
+    <t>0.3096,0.7917,0.0064,0.0035</t>
+  </si>
+  <si>
+    <t>0.2489,0.8129,0.0182,0.0014</t>
+  </si>
+  <si>
+    <t>0.0427,0.9306,0.0548,0.0011</t>
+  </si>
+  <si>
+    <t>0.0198,0.9708,0.0150,0.0004</t>
+  </si>
+  <si>
+    <t>0.2058,0.8602,0.0070,0.0009</t>
+  </si>
+  <si>
+    <t>0.4720,0.2662,0.3621,0.0585</t>
+  </si>
+  <si>
+    <t>0.1034,0.0254,0.8960,0.0113</t>
+  </si>
+  <si>
+    <t>0.2075,0.4235,0.4623,0.0437</t>
+  </si>
+  <si>
+    <t>0.1906,0.2787,0.6101,0.0398</t>
+  </si>
+  <si>
+    <t>0.2682,0.4802,0.2135,0.3940</t>
+  </si>
+  <si>
+    <t>0.0054,0.9746,0.0855,0.0010</t>
+  </si>
+  <si>
+    <t>0.0018,0.9831,0.0316,0.0026</t>
+  </si>
+  <si>
+    <t>0.0773,0.7466,0.2745,0.0588</t>
+  </si>
+  <si>
+    <t>0.0006,0.9664,0.7316,0.0002</t>
+  </si>
+  <si>
+    <t>0.0148,0.9091,0.3725,0.0013</t>
+  </si>
+  <si>
+    <t>0.3156,0.7479,0.0257,0.0027</t>
+  </si>
+  <si>
+    <t>0.0848,0.9087,0.0325,0.0014</t>
+  </si>
+  <si>
+    <t>0.9030,0.1019,0.0181,0.0028</t>
+  </si>
+  <si>
+    <t>0.9419,0.0294,0.0142,0.0102</t>
+  </si>
+  <si>
+    <t>0.9799,0.0126,0.0032,0.0020</t>
+  </si>
+  <si>
+    <t>0.8982,0.1036,0.0114,0.0055</t>
+  </si>
+  <si>
+    <t>0.9306,0.0733,0.0089,0.0037</t>
+  </si>
+  <si>
+    <t>0.8157,0.0800,0.1468,0.0069</t>
+  </si>
+  <si>
+    <t>0.9668,0.0286,0.0079,0.0020</t>
+  </si>
+  <si>
+    <t>0.9740,0.0067,0.0040,0.0083</t>
+  </si>
+  <si>
+    <t>0.0006,0.7701,0.9597,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.7219,0.9414,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.5959,0.9766,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.4117,0.9657,0.0002</t>
+  </si>
+  <si>
+    <t>0.5219,0.2245,0.3035,0.1856</t>
+  </si>
+  <si>
+    <t>0.2815,0.1628,0.6250,0.0853</t>
+  </si>
+  <si>
+    <t>0.2444,0.0232,0.8190,0.0205</t>
+  </si>
+  <si>
+    <t>0.5373,0.2171,0.3360,0.0478</t>
+  </si>
+  <si>
+    <t>0.0076,0.0019,0.0050,0.9936</t>
+  </si>
+  <si>
+    <t>0.0002,0.0019,0.0025,0.9994</t>
+  </si>
+  <si>
+    <t>0.0022,0.0093,0.0066,0.9963</t>
+  </si>
+  <si>
+    <t>0.0094,0.0023,0.0041,0.9941</t>
+  </si>
+  <si>
+    <t>0.0012,0.6939,0.9114,0.0034</t>
+  </si>
+  <si>
+    <t>0.9037,0.1024,0.0136,0.0045</t>
+  </si>
+  <si>
+    <t>0.1994,0.8471,0.0123,0.0054</t>
+  </si>
+  <si>
+    <t>0.8994,0.0791,0.0109,0.0123</t>
+  </si>
+  <si>
+    <t>0.8800,0.1447,0.0095,0.0044</t>
+  </si>
+  <si>
+    <t>0.8763,0.0538,0.0744,0.0178</t>
+  </si>
+  <si>
+    <t>0.1191,0.0513,0.0993,0.8615</t>
+  </si>
+  <si>
+    <t>0.9676,0.0194,0.0037,0.0040</t>
+  </si>
+  <si>
+    <t>0.0038,0.2259,0.9412,0.0203</t>
+  </si>
+  <si>
+    <t>0.7080,0.0040,0.0271,0.2828</t>
+  </si>
+  <si>
+    <t>0.8545,0.0087,0.0228,0.1037</t>
+  </si>
+  <si>
+    <t>0.0845,0.8944,0.0387,0.0041</t>
+  </si>
+  <si>
+    <t>0.2601,0.7377,0.0636,0.0141</t>
+  </si>
+  <si>
+    <t>0.3517,0.6494,0.1000,0.0192</t>
+  </si>
+  <si>
+    <t>0.3624,0.4677,0.2491,0.0470</t>
+  </si>
+  <si>
+    <t>0.5562,0.2223,0.3103,0.0106</t>
+  </si>
+  <si>
+    <t>0.3400,0.6374,0.0878,0.0064</t>
+  </si>
+  <si>
+    <t>0.9729,0.0186,0.0035,0.0030</t>
+  </si>
+  <si>
+    <t>0.9516,0.0321,0.0029,0.0061</t>
+  </si>
+  <si>
+    <t>0.9747,0.0151,0.0030,0.0035</t>
+  </si>
+  <si>
+    <t>0.9665,0.0097,0.0069,0.0108</t>
+  </si>
+  <si>
+    <t>0.9720,0.0174,0.0027,0.0030</t>
+  </si>
+  <si>
+    <t>0.9676,0.0272,0.0034,0.0024</t>
+  </si>
+  <si>
+    <t>0.9791,0.0099,0.0040,0.0029</t>
+  </si>
+  <si>
+    <t>0.9856,0.0066,0.0034,0.0018</t>
+  </si>
+  <si>
+    <t>0.0910,0.9036,0.0277,0.0021</t>
+  </si>
+  <si>
+    <t>0.6920,0.3637,0.0258,0.0024</t>
+  </si>
+  <si>
+    <t>0.2344,0.7920,0.0277,0.0014</t>
+  </si>
+  <si>
+    <t>0.3728,0.4295,0.2214,0.0041</t>
+  </si>
+  <si>
+    <t>0.6687,0.4609,0.0110,0.0034</t>
+  </si>
+  <si>
+    <t>0.5163,0.5783,0.0175,0.0058</t>
+  </si>
+  <si>
+    <t>0.9573,0.0339,0.0066,0.0036</t>
+  </si>
+  <si>
+    <t>0.5045,0.4996,0.0595,0.0063</t>
+  </si>
+  <si>
+    <t>0.0023,0.1191,0.9913,0.0005</t>
+  </si>
+  <si>
+    <t>0.7620,0.2631,0.0355,0.0031</t>
+  </si>
+  <si>
+    <t>0.0021,0.0437,0.9840,0.0022</t>
+  </si>
+  <si>
+    <t>0.0005,0.0901,0.9905,0.0020</t>
+  </si>
+  <si>
+    <t>0.0395,0.0080,0.9609,0.0094</t>
+  </si>
+  <si>
+    <t>0.0035,0.0619,0.9774,0.0062</t>
+  </si>
+  <si>
+    <t>0.0053,0.0117,0.9851,0.0050</t>
+  </si>
+  <si>
+    <t>0.0022,0.0061,0.9921,0.0024</t>
+  </si>
+  <si>
+    <t>0.0038,0.0267,0.9877,0.0016</t>
+  </si>
+  <si>
+    <t>0.2184,0.0329,0.8296,0.0177</t>
+  </si>
+  <si>
+    <t>0.0570,0.0145,0.8974,0.1049</t>
+  </si>
+  <si>
+    <t>0.2745,0.0308,0.8058,0.0126</t>
+  </si>
+  <si>
+    <t>0.0648,0.4620,0.6131,0.0096</t>
+  </si>
+  <si>
+    <t>0.1706,0.4219,0.5377,0.0414</t>
+  </si>
+  <si>
+    <t>0.2576,0.6294,0.1928,0.0941</t>
+  </si>
+  <si>
+    <t>0.4448,0.1049,0.5480,0.0450</t>
+  </si>
+  <si>
+    <t>0.1223,0.1004,0.7934,0.0077</t>
+  </si>
+  <si>
+    <t>0.6451,0.4690,0.0135,0.0016</t>
+  </si>
+  <si>
+    <t>0.4768,0.6194,0.0164,0.0010</t>
+  </si>
+  <si>
+    <t>0.5841,0.4235,0.0441,0.0015</t>
+  </si>
+  <si>
+    <t>0.9628,0.0237,0.0040,0.0051</t>
+  </si>
+  <si>
+    <t>0.6051,0.5031,0.0155,0.0019</t>
+  </si>
+  <si>
+    <t>0.3613,0.0327,0.7006,0.0336</t>
+  </si>
+  <si>
+    <t>0.4359,0.0531,0.6062,0.0612</t>
+  </si>
+  <si>
+    <t>0.4285,0.1688,0.5024,0.0821</t>
+  </si>
+  <si>
+    <t>0.2461,0.0636,0.7266,0.0396</t>
+  </si>
+  <si>
+    <t>0.3561,0.0239,0.7243,0.0306</t>
+  </si>
+  <si>
+    <t>0.1359,0.0937,0.7600,0.1483</t>
+  </si>
+  <si>
+    <t>0.0218,0.3225,0.8748,0.0147</t>
+  </si>
+  <si>
+    <t>0.0005,0.5905,0.9677,0.0002</t>
+  </si>
+  <si>
+    <t>0.0107,0.4538,0.8739,0.0055</t>
+  </si>
+  <si>
+    <t>0.0032,0.1852,0.9611,0.0041</t>
+  </si>
+  <si>
+    <t>0.9757,0.0109,0.0025,0.0053</t>
+  </si>
+  <si>
+    <t>0.9764,0.0216,0.0043,0.0012</t>
+  </si>
+  <si>
+    <t>0.9801,0.0205,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.9702,0.0297,0.0029,0.0016</t>
+  </si>
+  <si>
+    <t>0.9590,0.0386,0.0050,0.0025</t>
+  </si>
+  <si>
+    <t>0.9484,0.0525,0.0111,0.0018</t>
+  </si>
+  <si>
+    <t>0.9773,0.0109,0.0023,0.0041</t>
+  </si>
+  <si>
+    <t>0.9654,0.0352,0.0042,0.0023</t>
+  </si>
+  <si>
+    <t>0.0131,0.0069,0.9821,0.0039</t>
+  </si>
+  <si>
+    <t>0.1230,0.2684,0.7015,0.0075</t>
+  </si>
+  <si>
+    <t>0.8202,0.0513,0.1353,0.0405</t>
+  </si>
+  <si>
+    <t>0.0034,0.0406,0.9833,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.1066,0.9953,0.0006</t>
+  </si>
+  <si>
+    <t>0.0042,0.1223,0.9700,0.0022</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9988,0.0015</t>
+  </si>
+  <si>
+    <t>0.0833,0.0260,0.8951,0.0146</t>
+  </si>
+  <si>
+    <t>0.0007,0.0162,0.9938,0.0028</t>
+  </si>
+  <si>
+    <t>0.0015,0.0784,0.9849,0.0016</t>
+  </si>
+  <si>
+    <t>0.0751,0.0470,0.9007,0.0051</t>
+  </si>
+  <si>
+    <t>0.1439,0.0042,0.6406,0.2398</t>
+  </si>
+  <si>
+    <t>0.1431,0.0085,0.8865,0.0199</t>
+  </si>
+  <si>
+    <t>0.5069,0.0425,0.4713,0.0841</t>
+  </si>
+  <si>
+    <t>0.9586,0.0452,0.0049,0.0016</t>
+  </si>
+  <si>
+    <t>0.9819,0.0126,0.0034,0.0015</t>
+  </si>
+  <si>
+    <t>0.9695,0.0323,0.0035,0.0012</t>
+  </si>
+  <si>
+    <t>0.9512,0.0499,0.0075,0.0017</t>
+  </si>
+  <si>
+    <t>0.9738,0.0176,0.0050,0.0026</t>
+  </si>
+  <si>
+    <t>0.9413,0.0582,0.0106,0.0023</t>
+  </si>
+  <si>
+    <t>0.9871,0.0081,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.9582,0.0349,0.0126,0.0024</t>
+  </si>
+  <si>
+    <t>0.0118,0.2115,0.9396,0.0021</t>
+  </si>
+  <si>
+    <t>0.0017,0.0052,0.9912,0.0040</t>
+  </si>
+  <si>
+    <t>0.0043,0.4555,0.9214,0.0021</t>
+  </si>
+  <si>
+    <t>0.0257,0.0215,0.9579,0.0059</t>
+  </si>
+  <si>
+    <t>0.0044,0.0043,0.9775,0.0313</t>
+  </si>
+  <si>
+    <t>0.0961,0.0801,0.4492,0.5276</t>
+  </si>
+  <si>
+    <t>0.1159,0.0475,0.8505,0.0241</t>
+  </si>
+  <si>
+    <t>0.0045,0.0120,0.9746,0.0129</t>
+  </si>
+  <si>
+    <t>0.1642,0.0068,0.0287,0.8744</t>
+  </si>
+  <si>
+    <t>0.0014,0.0890,0.0008,0.9971</t>
+  </si>
+  <si>
+    <t>0.0039,0.0069,0.0037,0.9962</t>
+  </si>
+  <si>
+    <t>0.0022,0.0012,0.0154,0.9939</t>
+  </si>
+  <si>
+    <t>0.0020,0.0013,0.0049,0.9972</t>
+  </si>
+  <si>
+    <t>0.2201,0.1432,0.1634,0.7058</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,10 +2424,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,10 +2466,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,10 +2508,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,10 +2550,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,10 +2606,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3908,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,10 +4174,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,10 +4188,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,10 +4426,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4625,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,10 +4874,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
